--- a/光伏配储项目/电价数据/2026/筑梦站.xlsx
+++ b/光伏配储项目/电价数据/2026/筑梦站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.62064</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.83035</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.69812</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.60694</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.60688</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.61063</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43932</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43165</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40579</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4367799999999999</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42681</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43093</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42365</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45546</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.51663</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.19516</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.21574</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.21071</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17016</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.19614</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25153</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.0616</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15906</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24165</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24046</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24528</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22972</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.23515</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.87986</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.21924</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.5101600000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.5256799999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.53789</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6177999999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.6336000000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7262000000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.24995</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43488</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65454</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.96496</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.57008</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.30676</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.44086</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17332</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.30328</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.3812</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.56936</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.54448</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7847799999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.8369500000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.34835</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.14092</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86536</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7936299999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75363</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51464</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47676</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46474</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41443</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42388</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7003400000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74462</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86242</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9033</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48911</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.50718</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49677</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49697</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47961</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46223</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.56275</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.66207</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42886</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50929</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5778099999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.85265</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.06775</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.58052</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.93428</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.88842</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5569400000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.83505</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.24076</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05643</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40722</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50068</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58416</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.54365</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5377000000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.86397</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60609</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7824500000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8722300000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.23503</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.16015</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.89449</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.28536</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.18953</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.34803</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.1296</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.17425</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.73285</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.0651</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.8936000000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.0813</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.00372</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.09485</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.8971699999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44692</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.81245</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.83229</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44629</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44088</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33432</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50247</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4826</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4802</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44178</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41076</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42393</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4387799999999999</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46726</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44138</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.2088</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.26379</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.16194</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.53392</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.48568</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.48058</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.56604</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.57351</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.6587999999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.6236900000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.89781</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.57763</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.69577</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7756900000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.86222</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52276</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5205</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.77839</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.7127100000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64386</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.63428</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.4997200000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.57717</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45394</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5025500000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5111600000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.6105</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.57773</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.59933</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.23431</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6100599999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.77227</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47275</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51242</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57774</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.73578</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.74042</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.91126</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48458</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.61451</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.47525</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5757899999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.74153</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56235</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.9017500000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.70948</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.57724</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.51287</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.64476</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43588</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45413</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34161</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51418</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49129</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43905</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44516</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.48446</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.40893</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.49122</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.43019</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6555599999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.49622</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.50556</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.21819</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.41798</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5916699999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48954</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.4319</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.45174</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.42676</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.50492</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.7066699999999999</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40842</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48223</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.46952</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5323600000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.68529</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.54476</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.76542</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.58733</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.54635</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.50318</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.47725</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.4477</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30956</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24244</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26372</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.07429999999999999</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.2437</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.25798</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.18121</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24514</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.27076</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22325</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08454</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.17829</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01417</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26468</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45683</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.33085</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.45723</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.24853</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.21558</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.10456</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.22497</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24507</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27458</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.23401</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.25827</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.28687</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10344</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04398</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01178</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20958</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05094</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19572</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.06062</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06372999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06194</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32371</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30077</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42581</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45239</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7849400000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87191</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.76476</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.61219</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44874</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41931</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.50547</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5609</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.65437</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.86924</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.4967200000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.70135</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.45822</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83423</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.49785</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.51071</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.57723</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.5524</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.2343</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.28169</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33566</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.90547</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23478</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27223</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19431</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.24575</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.26267</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24819</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26843</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41173</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.41056</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.81174</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.3838</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08377</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.65332</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7422300000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6065900000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46417</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38644</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46804</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.23225</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.26854</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29878</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46969</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.0683</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14559</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26309</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27323</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02851</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25482</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.27039</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.48692</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.67338</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27458</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22685</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.23828</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.24449</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.23406</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.24102</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.2171</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25775</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.27498</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.20881</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.20932</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.10125</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.22734</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.10247</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.25261</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26784</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.25342</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.27587</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.22462</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.16287</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20609</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22387</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27918</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23707</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.24251</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.25382</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.26383</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22609</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.23237</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27508</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.25391</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27564</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.25081</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27212</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.24586</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22621</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.24767</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.25451</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.23253</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26924</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30842</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.48202</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.45487</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.47643</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44672</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.5527799999999999</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.48722</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.44013</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32736</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.44947</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.2443</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.50248</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.77318</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5849800000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5648500000000001</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.45682</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.53372</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.59794</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.47224</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.5150800000000001</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.47348</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.5376799999999999</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.5650299999999999</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.44599</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.9051</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.65579</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.51474</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.6121599999999999</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.56836</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.55396</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.55555</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.56757</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.58487</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.5149900000000001</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.63218</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.4631</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.48404</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.43145</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.74193</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.54192</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.5654199999999999</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5162100000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.49789</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.77622</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.47308</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.47649</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.41917</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49126</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22453</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.19617</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.25141</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.25716</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.24618</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.2487</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.24617</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.22255</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26925</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.25117</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.26154</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.26134</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.24001</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.22863</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26692</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.27305</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26481</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.23482</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33155</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.13343</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64059</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.96388</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.42453</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.31576</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.55711</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.43028</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.41709</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.55603</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.48419</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.45115</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.5216000000000001</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.5557799999999999</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.6325499999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.72377</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6812999999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.78185</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.47035</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.86794</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48149</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.77473</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.70786</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.56723</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.47811</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.60526</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.5258700000000001</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.43965</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3325</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.4372200000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.40322</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48617</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.48247</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.48149</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.50754</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.5290199999999999</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.56588</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.6646299999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.64489</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.44648</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.44936</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.45188</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.70043</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.89781</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.46719</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.45821</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.39594</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.52475</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.61214</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.45272</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.5314099999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5187999999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.47743</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.54157</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75548</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60753</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65444</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.47235</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.37736</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.14847</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.6445</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.55928</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.40762</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.48732</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.47812</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.48013</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.53495</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.23695</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27293</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25738</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.23746</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26807</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25745</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.26725</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.24221</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.23982</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.14844</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.13876</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.13771</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23987</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.13233</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.25813</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.23882</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.13116</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.22595</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.23212</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.25329</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.22885</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.23247</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.12702</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.23972</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.12649</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.11136</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.25423</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.23591</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.21598</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.10305</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27854</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11954</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2486</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.02309</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30172</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.19164</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27082</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01754</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28601</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25059</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25288</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25603</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.24974</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25911</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.29116</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.23463</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.23357</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.27336</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.26552</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.15726</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.23588</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.11474</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.24486</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25901</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.25289</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.14199</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.11694</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.11692</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.11508</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.11508</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.11619</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23997</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.10658</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.11508</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.11525</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22942</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.10877</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.10867</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.11968</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.07734000000000001</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.12073</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00282</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00016</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14159</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02177</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04084</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02932</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04602000000000001</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00092</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27444</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03851</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02227</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03638</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19969</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.11805</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.30123</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5396299999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.48243</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.22206</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.24339</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24223</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23868</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.12191</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.23471</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.22023</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.08968999999999999</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.10776</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.11684</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.13195</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.09723000000000001</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.14212</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.14912</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.16206</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42614</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27697</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.11653</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.5779</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.86811</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8581599999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10926</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.10689</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27382</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.14872</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.09483</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00087</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00048</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06691</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.11335</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.66791</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.5692999999999999</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.60875</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.09254</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97526</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.5775</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.7309099999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.6233200000000001</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83102</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82924</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8335199999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93126</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.56668</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6193500000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.5740599999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33586</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.47622</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.44594</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48283</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26775</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.26231</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.24227</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.25695</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.23491</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.23843</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.12419</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.25147</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.26203</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.28847</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40808</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.56721</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.49298</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42147</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32185</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.47825</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.7062</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.45634</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46925</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.4776</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.5737899999999999</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47486</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.83139</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8666</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.28769</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.51375</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.60414</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.59156</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.17767</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.9075599999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.57086</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.64904</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.49135</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.41893</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.4728</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45167</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.48743</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22319</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34003</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.47804</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.40808</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40257</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5042300000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.60542</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.39744</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.13447</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.64962</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.94026</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5312899999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.67787</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5806</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45708</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.8299299999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.75221</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.99839</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.90155</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.81213</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.7240800000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.43761</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.48349</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34449</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.1382</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.53761</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.48359</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.5313300000000001</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.9116299999999999</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.5440199999999999</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.47078</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.22835</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.68321</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.45159</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.45907</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.93469</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.56969</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.51131</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.44882</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.43562</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.5206799999999999</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.47618</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.41688</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.56956</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42738</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.7195</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.45828</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.5520499999999999</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43181</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.49428</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.71374</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.44136</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.48982</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.52447</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35033</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9226599999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.50025</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.52663</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.49967</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.5302899999999999</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41695</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.51171</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.52098</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.42889</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.54175</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.6332899999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.51707</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.48237</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.48324</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.46807</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35145</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40157</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37893</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17582</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19826</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14326</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04575</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12094</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22507</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14752</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14406</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28546</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19209</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22643</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15168</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15395</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19575</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14036</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.45164</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.59385</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45731</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41331</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40449</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37875</v>
       </c>
     </row>
   </sheetData>
